--- a/templates/OMS出库.xlsx
+++ b/templates/OMS出库.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14120"/>
+    <workbookView windowWidth="28260" windowHeight="12520"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t>请填写收件人信息格式(</t>
     </r>
     <r>
@@ -79,6 +85,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>商户编码</t>
     </r>
     <r>
@@ -94,6 +106,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>仓库</t>
     </r>
     <r>
@@ -112,6 +130,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>收件人信息</t>
     </r>
     <r>
@@ -127,7 +151,7 @@
   </si>
   <si>
     <r>
-      <t>商品编码</t>
+      <t>商家商品编码</t>
     </r>
     <r>
       <rPr>
@@ -142,6 +166,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>二级单位数量（</t>
     </r>
     <r>
@@ -165,6 +195,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>最小单位数量（</t>
     </r>
     <r>
@@ -390,14 +426,6 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Microsoft YaHei"/>
@@ -408,6 +436,14 @@
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="34">
@@ -733,7 +769,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/templates/OMS出库.xlsx
+++ b/templates/OMS出库.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>商家单号</t>
   </si>
@@ -72,6 +72,12 @@
     </r>
   </si>
   <si>
+    <t>门店名称</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>请填写商品编码</t>
   </si>
   <si>
@@ -79,9 +85,6 @@
   </si>
   <si>
     <t>请填写最小单位商品数量</t>
-  </si>
-  <si>
-    <t>外部单号</t>
   </si>
   <si>
     <r>
@@ -91,7 +94,7 @@
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>商户编码</t>
+      <t>外部单号</t>
     </r>
     <r>
       <rPr>
@@ -112,7 +115,7 @@
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>仓库</t>
+      <t>货主编码</t>
     </r>
     <r>
       <rPr>
@@ -126,9 +129,6 @@
     </r>
   </si>
   <si>
-    <t>物流公司</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -136,7 +136,7 @@
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>收件人信息</t>
+      <t>仓库编码</t>
     </r>
     <r>
       <rPr>
@@ -150,8 +150,17 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>商家商品编码</t>
+    <t>物流公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收件人信息</t>
     </r>
     <r>
       <rPr>
@@ -172,6 +181,27 @@
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
+      <t>商家商品编码</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>二级单位数量（</t>
     </r>
     <r>
@@ -221,12 +251,6 @@
       </rPr>
       <t>）</t>
     </r>
-  </si>
-  <si>
-    <t>门店名称</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -433,17 +457,17 @@
     </font>
     <font>
       <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1505,30 +1529,34 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="39" customHeight="1" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>15</v>
